--- a/server/plantillas/PLANTILLA_WHATSAPP_TIEMPOS.xlsx
+++ b/server/plantillas/PLANTILLA_WHATSAPP_TIEMPOS.xlsx
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -448,7 +448,7 @@
         <v>De dónde sale</v>
       </c>
       <c r="B2" t="str">
-        <v>Wolkvox: detalle de conversaciones de WhatsApp (hoja "HistQueue&lt;fecha&gt;"). La columna TIEMPO y la hoja de tabla dinámica se ignoran.</v>
+        <v>Wolkvox &gt; Reportes &gt; Skills &amp; Servicios &gt; 10. Detalle de llamadas contestadas (rango de fechas y SKILL = ALL). Se sube tal cual: CONN_ID, SKILL_ID, ANI, la columna TIEMPO y la hoja de tabla dinámica se ignoran.</v>
       </c>
     </row>
     <row r="3">
@@ -461,66 +461,57 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cómo se sube</v>
+        <v>Rangos</v>
       </c>
       <c r="B4" t="str">
-        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+        <v>El sistema clasifica cada WhatsApp contestado con ANSWER_TIME (segundos), sin fórmulas en el Excel: menos de 180 s = 0 a 3 minutos; menos de 300 s = 3 a 5 minutos; menos de 480 s = 5 a 8 minutos; menos de 600 s = 8 a 10 minutos; 600 s o más = 10 minutos en adelante.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Cómo se sube</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cargar Datos → cliente → este módulo. El sistema reconoce el archivo por sus columnas, no por el nombre de la hoja ni del archivo.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>Importante</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B6" t="str">
         <v>No cambie los nombres de las columnas. Los ejemplos de abajo son inventados: no los copie a la hoja de datos.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Columna</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Obligatoria</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Qué va</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Ejemplo (inventado)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>También se acepta como</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SKILL_NAME</v>
+        <v>Columna</v>
       </c>
       <c r="B8" t="str">
-        <v>Sí</v>
+        <v>Obligatoria</v>
       </c>
       <c r="C8" t="str">
-        <v>Cola (solo cuentan las que empiezan por WHATSAPP).</v>
+        <v>Qué va</v>
       </c>
       <c r="D8" t="str">
-        <v>WHATSAPP GENERAL</v>
+        <v>Ejemplo (inventado)</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>También se acepta como</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DATE</v>
+        <v>SKILL_NAME</v>
       </c>
       <c r="B9" t="str">
         <v>Sí</v>
       </c>
       <c r="C9" t="str">
-        <v>Fecha y hora de la conversación.</v>
+        <v>Cola (solo cuentan las que empiezan por WHATSAPP).</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-08-01 09:05</v>
+        <v>WHATSAPP GENERAL</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -528,16 +519,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>RESULT</v>
+        <v>DATE</v>
       </c>
       <c r="B10" t="str">
         <v>Sí</v>
       </c>
       <c r="C10" t="str">
-        <v>Resultado: solo cuentan las ANSWER (contestadas).</v>
+        <v>Fecha y hora de la conversación.</v>
       </c>
       <c r="D10" t="str">
-        <v>ANSWER</v>
+        <v>2026-08-01 09:05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -545,24 +536,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ANSWER_TIME</v>
+        <v>RESULT</v>
       </c>
       <c r="B11" t="str">
         <v>Sí</v>
       </c>
       <c r="C11" t="str">
-        <v>Segundos hasta que se contestó.</v>
-      </c>
-      <c r="D11">
-        <v>140</v>
+        <v>Resultado: solo cuentan las ANSWER (contestadas).</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ANSWER</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ANSWER_TIME</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sí</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Segundos hasta que se contestó (número, tal como sale de Wolkvox).</v>
+      </c>
+      <c r="D12">
+        <v>140</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>